--- a/artfynd/A 24114-2021 artfynd.xlsx
+++ b/artfynd/A 24114-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 24114-2021 artfynd.xlsx
+++ b/artfynd/A 24114-2021 artfynd.xlsx
@@ -13495,10 +13495,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120852342</v>
+        <v>120852338</v>
       </c>
       <c r="B112" t="n">
-        <v>90745</v>
+        <v>79682</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13511,21 +13511,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>3277</v>
+        <v>6458</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(O.F.Müll.:Fr.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -13535,10 +13535,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>704785</v>
+        <v>704782</v>
       </c>
       <c r="R112" t="n">
-        <v>7096451</v>
+        <v>7096446</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13604,7 +13604,7 @@
         <v>120852351</v>
       </c>
       <c r="B113" t="n">
-        <v>98105</v>
+        <v>98115</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13710,7 +13710,7 @@
         <v>120852360</v>
       </c>
       <c r="B114" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13813,10 +13813,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120852370</v>
+        <v>120852374</v>
       </c>
       <c r="B115" t="n">
-        <v>98092</v>
+        <v>79682</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13825,25 +13825,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -13853,10 +13853,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>704796</v>
+        <v>704819</v>
       </c>
       <c r="R115" t="n">
-        <v>7096447</v>
+        <v>7096417</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13919,10 +13919,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120852358</v>
+        <v>120852370</v>
       </c>
       <c r="B116" t="n">
-        <v>98092</v>
+        <v>98102</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13959,10 +13959,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>704787</v>
+        <v>704796</v>
       </c>
       <c r="R116" t="n">
-        <v>7096409</v>
+        <v>7096447</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -14025,10 +14025,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120852355</v>
+        <v>120852342</v>
       </c>
       <c r="B117" t="n">
-        <v>98071</v>
+        <v>90755</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -14037,25 +14037,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220787</v>
+        <v>3277</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(O.F.Müll.:Fr.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -14065,10 +14065,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>704795</v>
+        <v>704785</v>
       </c>
       <c r="R117" t="n">
-        <v>7096419</v>
+        <v>7096451</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -14095,17 +14095,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Yta med över 100 rosetter, enstaka blomstänglar.</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -14139,7 +14134,7 @@
         <v>120852343</v>
       </c>
       <c r="B118" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -14242,10 +14237,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120852359</v>
+        <v>120852358</v>
       </c>
       <c r="B119" t="n">
-        <v>98071</v>
+        <v>98102</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -14254,25 +14249,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -14282,10 +14277,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>704796</v>
+        <v>704787</v>
       </c>
       <c r="R119" t="n">
-        <v>7096420</v>
+        <v>7096409</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14318,11 +14313,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2024-08-21</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Ca 3 meter yta med riklig av rosetter och enstaka blomstänglar.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14353,10 +14343,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120852374</v>
+        <v>120852355</v>
       </c>
       <c r="B120" t="n">
-        <v>79679</v>
+        <v>98081</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -14365,25 +14355,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -14393,10 +14383,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>704819</v>
+        <v>704795</v>
       </c>
       <c r="R120" t="n">
-        <v>7096417</v>
+        <v>7096419</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14429,6 +14419,11 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Yta med över 100 rosetter, enstaka blomstänglar.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14459,10 +14454,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120852338</v>
+        <v>120852359</v>
       </c>
       <c r="B121" t="n">
-        <v>79679</v>
+        <v>98081</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14471,25 +14466,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -14499,10 +14494,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>704782</v>
+        <v>704796</v>
       </c>
       <c r="R121" t="n">
-        <v>7096446</v>
+        <v>7096420</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14529,12 +14524,17 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Ca 3 meter yta med riklig av rosetter och enstaka blomstänglar.</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14568,7 +14568,7 @@
         <v>120894832</v>
       </c>
       <c r="B122" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -14671,10 +14671,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120894845</v>
+        <v>120894879</v>
       </c>
       <c r="B123" t="n">
-        <v>98071</v>
+        <v>98102</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14683,25 +14683,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -14715,10 +14715,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>704798</v>
+        <v>704779</v>
       </c>
       <c r="R123" t="n">
-        <v>7096423</v>
+        <v>7096439</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14777,10 +14777,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120894882</v>
+        <v>120894845</v>
       </c>
       <c r="B124" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14812,7 +14812,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -14821,10 +14821,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>704775</v>
+        <v>704798</v>
       </c>
       <c r="R124" t="n">
-        <v>7096440</v>
+        <v>7096423</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14883,10 +14883,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120894879</v>
+        <v>120894882</v>
       </c>
       <c r="B125" t="n">
-        <v>98092</v>
+        <v>98081</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14895,30 +14895,30 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
@@ -14927,10 +14927,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>704779</v>
+        <v>704775</v>
       </c>
       <c r="R125" t="n">
-        <v>7096439</v>
+        <v>7096440</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14992,7 +14992,7 @@
         <v>120894840</v>
       </c>
       <c r="B126" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>

--- a/artfynd/A 24114-2021 artfynd.xlsx
+++ b/artfynd/A 24114-2021 artfynd.xlsx
@@ -13495,7 +13495,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120852338</v>
+        <v>120852374</v>
       </c>
       <c r="B112" t="n">
         <v>79682</v>
@@ -13535,10 +13535,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>704782</v>
+        <v>704819</v>
       </c>
       <c r="R112" t="n">
-        <v>7096446</v>
+        <v>7096417</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13565,12 +13565,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13601,10 +13601,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120852351</v>
+        <v>120852359</v>
       </c>
       <c r="B113" t="n">
-        <v>98115</v>
+        <v>98081</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13613,25 +13613,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -13641,10 +13641,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>704790</v>
+        <v>704796</v>
       </c>
       <c r="R113" t="n">
-        <v>7096472</v>
+        <v>7096420</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13677,6 +13677,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Ca 3 meter yta med riklig av rosetter och enstaka blomstänglar.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13707,10 +13712,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120852360</v>
+        <v>120852338</v>
       </c>
       <c r="B114" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13719,25 +13724,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -13747,10 +13752,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>704788</v>
+        <v>704782</v>
       </c>
       <c r="R114" t="n">
-        <v>7096475</v>
+        <v>7096446</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13777,12 +13782,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13813,10 +13818,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120852374</v>
+        <v>120852342</v>
       </c>
       <c r="B115" t="n">
-        <v>79682</v>
+        <v>90755</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13829,21 +13834,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6458</v>
+        <v>3277</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(O.F.Müll.:Fr.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -13853,10 +13858,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>704819</v>
+        <v>704785</v>
       </c>
       <c r="R115" t="n">
-        <v>7096417</v>
+        <v>7096451</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13883,12 +13888,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13919,10 +13924,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120852370</v>
+        <v>120852351</v>
       </c>
       <c r="B116" t="n">
-        <v>98102</v>
+        <v>98115</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13935,16 +13940,16 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>221952</v>
+        <v>219874</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -13959,10 +13964,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>704796</v>
+        <v>704790</v>
       </c>
       <c r="R116" t="n">
-        <v>7096447</v>
+        <v>7096472</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -14025,10 +14030,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120852342</v>
+        <v>120852358</v>
       </c>
       <c r="B117" t="n">
-        <v>90755</v>
+        <v>98102</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -14037,25 +14042,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>3277</v>
+        <v>221952</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(O.F.Müll.:Fr.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -14065,10 +14070,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>704785</v>
+        <v>704787</v>
       </c>
       <c r="R117" t="n">
-        <v>7096451</v>
+        <v>7096409</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -14095,12 +14100,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -14131,7 +14136,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120852343</v>
+        <v>120852360</v>
       </c>
       <c r="B118" t="n">
         <v>98081</v>
@@ -14171,10 +14176,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>704787</v>
+        <v>704788</v>
       </c>
       <c r="R118" t="n">
-        <v>7096449</v>
+        <v>7096475</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14201,12 +14206,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -14237,10 +14242,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120852358</v>
+        <v>120852355</v>
       </c>
       <c r="B119" t="n">
-        <v>98102</v>
+        <v>98081</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -14249,25 +14254,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -14277,10 +14282,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>704787</v>
+        <v>704795</v>
       </c>
       <c r="R119" t="n">
-        <v>7096409</v>
+        <v>7096419</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14313,6 +14318,11 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Yta med över 100 rosetter, enstaka blomstänglar.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14343,7 +14353,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120852355</v>
+        <v>120852343</v>
       </c>
       <c r="B120" t="n">
         <v>98081</v>
@@ -14383,10 +14393,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>704795</v>
+        <v>704787</v>
       </c>
       <c r="R120" t="n">
-        <v>7096419</v>
+        <v>7096449</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14413,17 +14423,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Yta med över 100 rosetter, enstaka blomstänglar.</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14454,10 +14459,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120852359</v>
+        <v>120852370</v>
       </c>
       <c r="B121" t="n">
-        <v>98081</v>
+        <v>98102</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14466,25 +14471,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -14497,7 +14502,7 @@
         <v>704796</v>
       </c>
       <c r="R121" t="n">
-        <v>7096420</v>
+        <v>7096447</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14530,11 +14535,6 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2024-08-21</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Ca 3 meter yta med riklig av rosetter och enstaka blomstänglar.</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14565,10 +14565,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120894832</v>
+        <v>120894879</v>
       </c>
       <c r="B122" t="n">
-        <v>98081</v>
+        <v>98102</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -14577,30 +14577,30 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -14609,10 +14609,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>704810</v>
+        <v>704779</v>
       </c>
       <c r="R122" t="n">
-        <v>7096464</v>
+        <v>7096439</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14671,10 +14671,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120894879</v>
+        <v>120894832</v>
       </c>
       <c r="B123" t="n">
-        <v>98102</v>
+        <v>98081</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14683,30 +14683,30 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -14715,10 +14715,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>704779</v>
+        <v>704810</v>
       </c>
       <c r="R123" t="n">
-        <v>7096439</v>
+        <v>7096464</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14777,7 +14777,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120894845</v>
+        <v>120894882</v>
       </c>
       <c r="B124" t="n">
         <v>98081</v>
@@ -14812,7 +14812,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -14821,10 +14821,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>704798</v>
+        <v>704775</v>
       </c>
       <c r="R124" t="n">
-        <v>7096423</v>
+        <v>7096440</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14883,7 +14883,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120894882</v>
+        <v>120894845</v>
       </c>
       <c r="B125" t="n">
         <v>98081</v>
@@ -14918,7 +14918,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
@@ -14927,10 +14927,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>704775</v>
+        <v>704798</v>
       </c>
       <c r="R125" t="n">
-        <v>7096440</v>
+        <v>7096423</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>

--- a/artfynd/A 24114-2021 artfynd.xlsx
+++ b/artfynd/A 24114-2021 artfynd.xlsx
@@ -14777,10 +14777,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120894882</v>
+        <v>120894840</v>
       </c>
       <c r="B124" t="n">
-        <v>98081</v>
+        <v>78601</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14789,42 +14789,38 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>lokälsberget, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>704775</v>
+        <v>704803</v>
       </c>
       <c r="R124" t="n">
-        <v>7096440</v>
+        <v>7096480</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14883,7 +14879,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120894845</v>
+        <v>120894882</v>
       </c>
       <c r="B125" t="n">
         <v>98081</v>
@@ -14918,7 +14914,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
@@ -14927,10 +14923,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>704798</v>
+        <v>704775</v>
       </c>
       <c r="R125" t="n">
-        <v>7096423</v>
+        <v>7096440</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14989,10 +14985,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120894840</v>
+        <v>120894845</v>
       </c>
       <c r="B126" t="n">
-        <v>78601</v>
+        <v>98081</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -15001,38 +14997,42 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>lokälsberget, Ång</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>704803</v>
+        <v>704798</v>
       </c>
       <c r="R126" t="n">
-        <v>7096480</v>
+        <v>7096423</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
